--- a/Zinc/6. Sensitivity analyses/Carbonate_system_SA.xlsx
+++ b/Zinc/6. Sensitivity analyses/Carbonate_system_SA.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t xml:space="preserve">BL_ZnOH_nmol_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBL_Zn_nmol_kg</t>
   </si>
   <si>
     <t xml:space="preserve">positive</t>
@@ -503,22 +506,22 @@
         <v>-15.381072415721</v>
       </c>
       <c r="C2" t="n">
-        <v>1.11777365141558</v>
+        <v>1.10740394632106</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2738697025868</v>
+        <v>4.08845801658225</v>
       </c>
       <c r="E2" t="n">
-        <v>7.65577750611466</v>
+        <v>7.19291651732251</v>
       </c>
       <c r="F2" t="n">
-        <v>10.4756976426756</v>
+        <v>9.4508774139967</v>
       </c>
       <c r="G2" t="n">
-        <v>80.4969886303297</v>
+        <v>73.353589868929</v>
       </c>
       <c r="H2" t="n">
-        <v>9.35792399126005</v>
+        <v>8.34347346767564</v>
       </c>
     </row>
     <row r="3">
@@ -529,22 +532,22 @@
         <v>-5.49299405960824</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0257953068627529</v>
+        <v>0.0270079410225051</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0770880269340695</v>
+        <v>0.0790807003214765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0465249346547246</v>
+        <v>0.0447387392578329</v>
       </c>
       <c r="F3" t="n">
-        <v>0.155558631947939</v>
+        <v>0.165577909022608</v>
       </c>
       <c r="G3" t="n">
         <v>0.83585205423731</v>
       </c>
       <c r="H3" t="n">
-        <v>0.129763325085186</v>
+        <v>0.138569968000103</v>
       </c>
     </row>
     <row r="4">
@@ -555,22 +558,22 @@
         <v>-85.7043005453311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00316190053740315</v>
+        <v>0.00424161573919779</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0138660610771168</v>
+        <v>0.0170083860190352</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.56435077171495</v>
+        <v>-0.612409435263703</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0407038500127574</v>
+        <v>0.0451781476812348</v>
       </c>
       <c r="G4" t="n">
         <v>1.0109513226553</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0375419494753542</v>
+        <v>0.040936531942037</v>
       </c>
     </row>
     <row r="5">
@@ -581,22 +584,22 @@
         <v>-15.802621433636</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.33595440160652</v>
+        <v>-3.39695543916108</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.83906102846354</v>
+        <v>-1.89587111287804</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.683237277670077</v>
+        <v>-0.638358226848564</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.811594496469281</v>
+        <v>-0.891575759401355</v>
       </c>
       <c r="G5" t="n">
         <v>130.893749172856</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52435990513724</v>
+        <v>2.50537967975972</v>
       </c>
     </row>
     <row r="6">
@@ -607,22 +610,22 @@
         <v>-109.229246092468</v>
       </c>
       <c r="C6" t="n">
-        <v>-21.7978565197897</v>
+        <v>-20.4182859508962</v>
       </c>
       <c r="D6" t="n">
-        <v>-13.8015368023048</v>
+        <v>-13.5674584900158</v>
       </c>
       <c r="E6" t="n">
-        <v>-15.2153186786413</v>
+        <v>-14.5292887360146</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.81525452844523</v>
+        <v>-4.76531791804292</v>
       </c>
       <c r="G6" t="n">
         <v>29.1749131520192</v>
       </c>
       <c r="H6" t="n">
-        <v>16.9826019913444</v>
+        <v>15.6529680328532</v>
       </c>
     </row>
     <row r="7">
@@ -633,22 +636,22 @@
         <v>-0.571250935443854</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0168285281543228</v>
+        <v>0.0166526306633053</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0530505916973562</v>
+        <v>0.0527266910688163</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0735851705153305</v>
+        <v>0.0706726741836986</v>
       </c>
       <c r="F7" t="n">
-        <v>0.111366284250014</v>
+        <v>0.109034264256236</v>
       </c>
       <c r="G7" t="n">
         <v>0.69407146696676</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0945377560956912</v>
+        <v>0.0923816335929312</v>
       </c>
     </row>
     <row r="8">
@@ -659,22 +662,22 @@
         <v>-0.0231323189769928</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000403489036886887</v>
+        <v>0.000410764358724923</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00219198444117997</v>
+        <v>0.00217858803913672</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00511329108540233</v>
+        <v>0.00438586885221351</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00618403722327243</v>
+        <v>0.00586135426219192</v>
       </c>
       <c r="G8" t="n">
         <v>0.158968435637341</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00578054818638554</v>
+        <v>0.005450589903467</v>
       </c>
     </row>
     <row r="9">
@@ -691,16 +694,16 @@
         <v>0.000000000000880120171796126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000000000355259072407013</v>
+        <v>0.00000000000273635064298376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00000000000307711187869726</v>
+        <v>0.00000000000263374307040854</v>
       </c>
       <c r="G9" t="n">
         <v>0.0000000000865958839670043</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00000000000307711187869726</v>
+        <v>0.00000000000263374307040854</v>
       </c>
     </row>
     <row r="10">
@@ -711,22 +714,22 @@
         <v>-97.581557759257</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8918220209589</v>
+        <v>3.87470273193977</v>
       </c>
       <c r="D10" t="n">
-        <v>8.5144053293994</v>
+        <v>8.3807009873634</v>
       </c>
       <c r="E10" t="n">
-        <v>8.68175060984978</v>
+        <v>8.46701689071949</v>
       </c>
       <c r="F10" t="n">
-        <v>13.5557802667731</v>
+        <v>13.4438613336049</v>
       </c>
       <c r="G10" t="n">
         <v>51.366511162332</v>
       </c>
       <c r="H10" t="n">
-        <v>9.6639582458142</v>
+        <v>9.5691586016651</v>
       </c>
     </row>
     <row r="11">
@@ -737,22 +740,22 @@
         <v>-4227182.21670948</v>
       </c>
       <c r="C11" t="n">
-        <v>-2493166.61211196</v>
+        <v>-2473094.96990056</v>
       </c>
       <c r="D11" t="n">
-        <v>-1872790.01693242</v>
+        <v>-1833514.81973659</v>
       </c>
       <c r="E11" t="n">
-        <v>-1518543.09884923</v>
+        <v>-1473709.80053903</v>
       </c>
       <c r="F11" t="n">
-        <v>-1128984.82984747</v>
+        <v>-1124767.6302446</v>
       </c>
       <c r="G11" t="n">
         <v>24233975.680545</v>
       </c>
       <c r="H11" t="n">
-        <v>1364181.78226449</v>
+        <v>1348327.33965596</v>
       </c>
     </row>
     <row r="12">
@@ -760,25 +763,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>-1313014.69809841</v>
+        <v>-1207203.67522153</v>
       </c>
       <c r="C12" t="n">
-        <v>-197739.085706416</v>
+        <v>-172907.286469126</v>
       </c>
       <c r="D12" t="n">
-        <v>-95842.0005190418</v>
+        <v>-91990.8343348651</v>
       </c>
       <c r="E12" t="n">
-        <v>-164673.494991025</v>
+        <v>-139712.49602734</v>
       </c>
       <c r="F12" t="n">
-        <v>-42478.1460424129</v>
+        <v>-40741.5441259218</v>
       </c>
       <c r="G12" t="n">
         <v>24084.8287376139</v>
       </c>
       <c r="H12" t="n">
-        <v>155260.939664003</v>
+        <v>132165.742343204</v>
       </c>
     </row>
     <row r="13">
@@ -789,22 +792,22 @@
         <v>-0.000000000070924223479098</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.00000000000279779978438966</v>
+        <v>-0.00000000000262857071767259</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00000000000141658355360436</v>
+        <v>-0.00000000000130761341311364</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0000000000025880822096539</v>
+        <v>-0.00000000000229376184301506</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.000000000000570135650840912</v>
+        <v>-0.000000000000552421495224276</v>
       </c>
       <c r="G13" t="n">
         <v>0.00000000000115165594031759</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00000000000222766413354874</v>
+        <v>0.00000000000207614922244831</v>
       </c>
     </row>
     <row r="14">
@@ -812,25 +815,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.000000000066761954034308</v>
+        <v>-0.0000000000517102977273062</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0000000000010559887209922</v>
+        <v>-0.00000000000087386461837399</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.000000000000265132590904378</v>
+        <v>-0.000000000000238892906251516</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.00000000000172018490808414</v>
+        <v>-0.00000000000118055549151304</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0000000000000725538472379065</v>
+        <v>-0.0000000000000701875926883767</v>
       </c>
       <c r="G14" t="n">
         <v>0.0000000000000611176612752003</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000000000000983434873754293</v>
+        <v>0.000000000000803677025685613</v>
       </c>
     </row>
     <row r="15">
@@ -841,22 +844,22 @@
         <v>-24138.0032548477</v>
       </c>
       <c r="C15" t="n">
-        <v>-9599.1464377221</v>
+        <v>-9461.29996748369</v>
       </c>
       <c r="D15" t="n">
-        <v>-6358.760614944</v>
+        <v>-6315.8180410028</v>
       </c>
       <c r="E15" t="n">
-        <v>-6179.6649983508</v>
+        <v>-6102.88686184024</v>
       </c>
       <c r="F15" t="n">
-        <v>-3015.12088185519</v>
+        <v>-3004.0287981592</v>
       </c>
       <c r="G15" t="n">
         <v>42080.2907683537</v>
       </c>
       <c r="H15" t="n">
-        <v>6584.02555586691</v>
+        <v>6457.27116932449</v>
       </c>
     </row>
     <row r="16">
@@ -867,22 +870,22 @@
         <v>-3282.23450196674</v>
       </c>
       <c r="C16" t="n">
-        <v>-1196.01887149657</v>
+        <v>-1229.59306736447</v>
       </c>
       <c r="D16" t="n">
-        <v>-648.931790081519</v>
+        <v>-705.962598601672</v>
       </c>
       <c r="E16" t="n">
-        <v>1151.90337245332</v>
+        <v>1268.56071980857</v>
       </c>
       <c r="F16" t="n">
-        <v>-221.536945455015</v>
+        <v>-264.0877254656</v>
       </c>
       <c r="G16" t="n">
         <v>209925.550734624</v>
       </c>
       <c r="H16" t="n">
-        <v>974.481926041555</v>
+        <v>965.505341898873</v>
       </c>
     </row>
     <row r="17">
@@ -893,22 +896,22 @@
         <v>-9608.2221716642</v>
       </c>
       <c r="C17" t="n">
-        <v>74.9686535073122</v>
+        <v>75.8539613343625</v>
       </c>
       <c r="D17" t="n">
-        <v>168.75264918781</v>
+        <v>175.162313098555</v>
       </c>
       <c r="E17" t="n">
-        <v>126.507173616408</v>
+        <v>125.69766403766</v>
       </c>
       <c r="F17" t="n">
-        <v>292.137087853915</v>
+        <v>299.282078231045</v>
       </c>
       <c r="G17" t="n">
         <v>1286.1855793744</v>
       </c>
       <c r="H17" t="n">
-        <v>217.168434346603</v>
+        <v>223.428116896683</v>
       </c>
     </row>
     <row r="18">
@@ -916,25 +919,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>-61146.1307471473</v>
+        <v>-60168.9107497805</v>
       </c>
       <c r="C18" t="n">
-        <v>-26799.8991603235</v>
+        <v>-26197.1836152952</v>
       </c>
       <c r="D18" t="n">
-        <v>-17873.0415427708</v>
+        <v>-17242.2519426618</v>
       </c>
       <c r="E18" t="n">
-        <v>-17069.2107586652</v>
+        <v>-16474.0117036085</v>
       </c>
       <c r="F18" t="n">
-        <v>-7206.60960951136</v>
+        <v>-7198.11714589014</v>
       </c>
       <c r="G18" t="n">
         <v>82096.3869045956</v>
       </c>
       <c r="H18" t="n">
-        <v>19593.2895508122</v>
+        <v>18999.0664694051</v>
       </c>
     </row>
     <row r="19">
@@ -945,22 +948,22 @@
         <v>-18969.0745173721</v>
       </c>
       <c r="C19" t="n">
-        <v>-5278.54226817226</v>
+        <v>-5554.18162662136</v>
       </c>
       <c r="D19" t="n">
-        <v>-2782.78756127293</v>
+        <v>-3154.29068109552</v>
       </c>
       <c r="E19" t="n">
-        <v>2641.14583495855</v>
+        <v>2975.43152812408</v>
       </c>
       <c r="F19" t="n">
-        <v>-1088.53318891989</v>
+        <v>-1174.60863879871</v>
       </c>
       <c r="G19" t="n">
         <v>607018.257142045</v>
       </c>
       <c r="H19" t="n">
-        <v>4190.00907925238</v>
+        <v>4379.57298782265</v>
       </c>
     </row>
     <row r="20">
@@ -971,22 +974,22 @@
         <v>-26551.9665845205</v>
       </c>
       <c r="C20" t="n">
-        <v>197.264398593687</v>
+        <v>195.742700270798</v>
       </c>
       <c r="D20" t="n">
-        <v>432.556589657876</v>
+        <v>446.10305849346</v>
       </c>
       <c r="E20" t="n">
-        <v>385.516662208969</v>
+        <v>374.581028901261</v>
       </c>
       <c r="F20" t="n">
-        <v>932.72888079805</v>
+        <v>964.757873589374</v>
       </c>
       <c r="G20" t="n">
         <v>2700.06785285659</v>
       </c>
       <c r="H20" t="n">
-        <v>735.464482204363</v>
+        <v>769.015173318576</v>
       </c>
     </row>
     <row r="21">
@@ -997,22 +1000,22 @@
         <v>-3776.70229329517</v>
       </c>
       <c r="C21" t="n">
-        <v>-281.150423538026</v>
+        <v>-230.704207068028</v>
       </c>
       <c r="D21" t="n">
-        <v>-123.178033062236</v>
+        <v>-105.598753436724</v>
       </c>
       <c r="E21" t="n">
-        <v>-253.078788828087</v>
+        <v>-208.377938380848</v>
       </c>
       <c r="F21" t="n">
-        <v>-47.4446855460169</v>
+        <v>-44.2765467823153</v>
       </c>
       <c r="G21" t="n">
         <v>1206.82438633709</v>
       </c>
       <c r="H21" t="n">
-        <v>233.705737992009</v>
+        <v>186.427660285712</v>
       </c>
     </row>
     <row r="22">
@@ -1023,22 +1026,22 @@
         <v>-494.94423254304</v>
       </c>
       <c r="C22" t="n">
-        <v>-47.1813650076538</v>
+        <v>-44.89926513922</v>
       </c>
       <c r="D22" t="n">
-        <v>-22.112455736255</v>
+        <v>-20.6193138119147</v>
       </c>
       <c r="E22" t="n">
-        <v>-36.2202563760765</v>
+        <v>-33.4810040671611</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.01857289837</v>
+        <v>-9.61072461891706</v>
       </c>
       <c r="G22" t="n">
         <v>203.229325312903</v>
       </c>
       <c r="H22" t="n">
-        <v>37.1627921092838</v>
+        <v>35.2885405203029</v>
       </c>
     </row>
     <row r="23">
@@ -1049,22 +1052,22 @@
         <v>-102.264804291401</v>
       </c>
       <c r="C23" t="n">
-        <v>-19.5719118759001</v>
+        <v>-19.1487886588901</v>
       </c>
       <c r="D23" t="n">
         <v>-10.2467260188991</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.69581371711186</v>
+        <v>-9.01334784035381</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.68587592291226</v>
+        <v>-5.52262515536765</v>
       </c>
       <c r="G23" t="n">
         <v>500.90705827621</v>
       </c>
       <c r="H23" t="n">
-        <v>13.8860359529879</v>
+        <v>13.6261635035225</v>
       </c>
     </row>
     <row r="24">
@@ -1075,22 +1078,22 @@
         <v>-270.7711246331</v>
       </c>
       <c r="C24" t="n">
-        <v>8.94395313366653</v>
+        <v>8.7756246713866</v>
       </c>
       <c r="D24" t="n">
-        <v>23.0282282132065</v>
+        <v>21.4617728033775</v>
       </c>
       <c r="E24" t="n">
-        <v>41.4008176779739</v>
+        <v>37.2854030995778</v>
       </c>
       <c r="F24" t="n">
-        <v>55.3763186417198</v>
+        <v>49.0362879190792</v>
       </c>
       <c r="G24" t="n">
-        <v>880.741936271101</v>
+        <v>388.5656951752</v>
       </c>
       <c r="H24" t="n">
-        <v>46.4323655080533</v>
+        <v>40.2606632476926</v>
       </c>
     </row>
     <row r="25">
@@ -1098,25 +1101,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>-249.336949309505</v>
+        <v>-243.8810042804</v>
       </c>
       <c r="C25" t="n">
-        <v>1.55359902720419</v>
+        <v>1.48084788875732</v>
       </c>
       <c r="D25" t="n">
-        <v>3.79433373609575</v>
+        <v>3.72025255046535</v>
       </c>
       <c r="E25" t="n">
-        <v>8.18113633257685</v>
+        <v>7.35446093787528</v>
       </c>
       <c r="F25" t="n">
-        <v>10.8554871758317</v>
+        <v>10.5666835281681</v>
       </c>
       <c r="G25" t="n">
-        <v>201.74297787889</v>
+        <v>174.24849829695</v>
       </c>
       <c r="H25" t="n">
-        <v>9.30188814862755</v>
+        <v>9.08583563941075</v>
       </c>
     </row>
     <row r="26">
@@ -1127,22 +1130,22 @@
         <v>-0.000166156316777285</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0000148828201106729</v>
+        <v>0.0000148130028443935</v>
       </c>
       <c r="D26" t="n">
-        <v>0.000050759174528211</v>
+        <v>0.000049342230092212</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0000946307545408682</v>
+        <v>0.0000912363122630225</v>
       </c>
       <c r="F26" t="n">
-        <v>0.000121797996049185</v>
+        <v>0.000116417203791951</v>
       </c>
       <c r="G26" t="n">
         <v>0.00092757985648147</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000106915175938513</v>
+        <v>0.000101604200947557</v>
       </c>
     </row>
     <row r="27">
@@ -1153,22 +1156,22 @@
         <v>-0.109027728881147</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00168027332012449</v>
+        <v>0.001653030498276</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00233206263228</v>
+        <v>0.00230556175465296</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00125253556633626</v>
+        <v>0.00117542274184975</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00268975384169451</v>
+        <v>0.00267316950659274</v>
       </c>
       <c r="G27" t="n">
         <v>0.00376100968933102</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00100948052157002</v>
+        <v>0.00102013900831674</v>
       </c>
     </row>
     <row r="28">
@@ -1179,22 +1182,22 @@
         <v>-0.0017941493697866</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.000290848715286473</v>
+        <v>-0.00026339583930785</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.000137405232287995</v>
+        <v>-0.00012296699812747</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.000209181248637458</v>
+        <v>-0.000187188550392714</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0000693654723593524</v>
+        <v>-0.000064127783426345</v>
       </c>
       <c r="G28" t="n">
         <v>0.000125247228046799</v>
       </c>
       <c r="H28" t="n">
-        <v>0.000221483242927121</v>
+        <v>0.000199268055881505</v>
       </c>
     </row>
     <row r="29">
@@ -1205,22 +1208,22 @@
         <v>-0.005958297114659</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0001198522871223</v>
+        <v>0.0001191779108973</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001891822154787</v>
+        <v>0.000188965490807203</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000184616772291127</v>
+        <v>0.00018274002189702</v>
       </c>
       <c r="F29" t="n">
-        <v>0.000281654918106328</v>
+        <v>0.000277247300267198</v>
       </c>
       <c r="G29" t="n">
         <v>0.000804813653468697</v>
       </c>
       <c r="H29" t="n">
-        <v>0.000161802630984028</v>
+        <v>0.000158069389369898</v>
       </c>
     </row>
     <row r="30">
@@ -1228,25 +1231,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.0009669568151996</v>
+        <v>-0.000768383680073901</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.000235672267313049</v>
+        <v>-0.000237188667747782</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.000140690270800074</v>
+        <v>-0.00014240422956379</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000196954377965168</v>
+        <v>0.0000379878735025674</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0000648008270598475</v>
+        <v>-0.0000642475570943851</v>
       </c>
       <c r="G30" t="n">
         <v>0.0242187366642834</v>
       </c>
       <c r="H30" t="n">
-        <v>0.000170871440253202</v>
+        <v>0.000172941110653397</v>
       </c>
     </row>
     <row r="31">
@@ -1257,22 +1260,48 @@
         <v>-0.00166305449481691</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0000125750804166047</v>
+        <v>0.0000135182660603646</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0000320418833748018</v>
+        <v>0.0000343397348691504</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0000266182853147252</v>
+        <v>0.000026697958113284</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0000631734730672352</v>
+        <v>0.0000653921725275695</v>
       </c>
       <c r="G31" t="n">
         <v>0.00029198909318277</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0000505983926506305</v>
+        <v>0.0000518739064672049</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.00174568296133969</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0000334219611475955</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0000866868924677502</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.000117934270376307</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.000177135509937369</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.000996568571434058</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.000143713548789773</v>
       </c>
     </row>
   </sheetData>
@@ -1320,22 +1349,22 @@
         <v>-1538.1072415721</v>
       </c>
       <c r="C2" t="n">
-        <v>111.777365141558</v>
+        <v>110.740394632106</v>
       </c>
       <c r="D2" t="n">
-        <v>427.38697025868</v>
+        <v>408.845801658225</v>
       </c>
       <c r="E2" t="n">
-        <v>765.577750611466</v>
+        <v>719.291651732251</v>
       </c>
       <c r="F2" t="n">
-        <v>1047.56976426756</v>
+        <v>945.08774139967</v>
       </c>
       <c r="G2" t="n">
-        <v>8049.69886303297</v>
+        <v>7335.3589868929</v>
       </c>
       <c r="H2" t="n">
-        <v>935.792399126005</v>
+        <v>834.347346767564</v>
       </c>
     </row>
     <row r="3">
@@ -1346,22 +1375,22 @@
         <v>-549.299405960824</v>
       </c>
       <c r="C3" t="n">
-        <v>2.57953068627529</v>
+        <v>2.70079410225051</v>
       </c>
       <c r="D3" t="n">
-        <v>7.70880269340695</v>
+        <v>7.90807003214765</v>
       </c>
       <c r="E3" t="n">
-        <v>4.65249346547246</v>
+        <v>4.47387392578329</v>
       </c>
       <c r="F3" t="n">
-        <v>15.5558631947939</v>
+        <v>16.5577909022608</v>
       </c>
       <c r="G3" t="n">
         <v>83.585205423731</v>
       </c>
       <c r="H3" t="n">
-        <v>12.9763325085186</v>
+        <v>13.8569968000103</v>
       </c>
     </row>
     <row r="4">
@@ -1372,22 +1401,22 @@
         <v>-8570.43005453311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.316190053740315</v>
+        <v>0.424161573919779</v>
       </c>
       <c r="D4" t="n">
-        <v>1.38660610771168</v>
+        <v>1.70083860190352</v>
       </c>
       <c r="E4" t="n">
-        <v>-56.435077171495</v>
+        <v>-61.2409435263703</v>
       </c>
       <c r="F4" t="n">
-        <v>4.07038500127573</v>
+        <v>4.51781476812348</v>
       </c>
       <c r="G4" t="n">
         <v>101.09513226553</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75419494753542</v>
+        <v>4.0936531942037</v>
       </c>
     </row>
     <row r="5">
@@ -1398,22 +1427,22 @@
         <v>-1580.2621433636</v>
       </c>
       <c r="C5" t="n">
-        <v>-333.595440160652</v>
+        <v>-339.695543916108</v>
       </c>
       <c r="D5" t="n">
-        <v>-183.906102846354</v>
+        <v>-189.587111287804</v>
       </c>
       <c r="E5" t="n">
-        <v>-68.3237277670077</v>
+        <v>-63.8358226848564</v>
       </c>
       <c r="F5" t="n">
-        <v>-81.1594496469281</v>
+        <v>-89.1575759401355</v>
       </c>
       <c r="G5" t="n">
         <v>13089.3749172856</v>
       </c>
       <c r="H5" t="n">
-        <v>252.435990513724</v>
+        <v>250.537967975972</v>
       </c>
     </row>
     <row r="6">
@@ -1424,22 +1453,22 @@
         <v>-10922.9246092468</v>
       </c>
       <c r="C6" t="n">
-        <v>-2179.78565197896</v>
+        <v>-2041.82859508962</v>
       </c>
       <c r="D6" t="n">
-        <v>-1380.15368023048</v>
+        <v>-1356.74584900158</v>
       </c>
       <c r="E6" t="n">
-        <v>-1521.53186786413</v>
+        <v>-1452.92887360146</v>
       </c>
       <c r="F6" t="n">
-        <v>-481.525452844523</v>
+        <v>-476.531791804292</v>
       </c>
       <c r="G6" t="n">
         <v>2917.49131520192</v>
       </c>
       <c r="H6" t="n">
-        <v>1698.26019913444</v>
+        <v>1565.29680328532</v>
       </c>
     </row>
     <row r="7">
@@ -1450,22 +1479,22 @@
         <v>-57.1250935443854</v>
       </c>
       <c r="C7" t="n">
-        <v>1.68285281543228</v>
+        <v>1.66526306633053</v>
       </c>
       <c r="D7" t="n">
-        <v>5.30505916973562</v>
+        <v>5.27266910688163</v>
       </c>
       <c r="E7" t="n">
-        <v>7.35851705153305</v>
+        <v>7.06726741836986</v>
       </c>
       <c r="F7" t="n">
-        <v>11.1366284250014</v>
+        <v>10.9034264256236</v>
       </c>
       <c r="G7" t="n">
         <v>69.407146696676</v>
       </c>
       <c r="H7" t="n">
-        <v>9.45377560956912</v>
+        <v>9.23816335929312</v>
       </c>
     </row>
     <row r="8">
@@ -1476,22 +1505,22 @@
         <v>-2.31323189769928</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0403489036886887</v>
+        <v>0.0410764358724923</v>
       </c>
       <c r="D8" t="n">
-        <v>0.219198444117997</v>
+        <v>0.217858803913672</v>
       </c>
       <c r="E8" t="n">
-        <v>0.511329108540233</v>
+        <v>0.438586885221351</v>
       </c>
       <c r="F8" t="n">
-        <v>0.618403722327242</v>
+        <v>0.586135426219192</v>
       </c>
       <c r="G8" t="n">
         <v>15.8968435637341</v>
       </c>
       <c r="H8" t="n">
-        <v>0.578054818638554</v>
+        <v>0.5450589903467</v>
       </c>
     </row>
     <row r="9">
@@ -1508,16 +1537,16 @@
         <v>0.0000000000880120171796126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000000000355259072407013</v>
+        <v>0.000000000273635064298376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000000000307711187869726</v>
+        <v>0.000000000263374307040854</v>
       </c>
       <c r="G9" t="n">
         <v>0.00000000865958839670043</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000000000307711187869726</v>
+        <v>0.000000000263374307040854</v>
       </c>
     </row>
     <row r="10">
@@ -1528,22 +1557,22 @@
         <v>-9758.1557759257</v>
       </c>
       <c r="C10" t="n">
-        <v>389.18220209589</v>
+        <v>387.470273193978</v>
       </c>
       <c r="D10" t="n">
-        <v>851.44053293994</v>
+        <v>838.07009873634</v>
       </c>
       <c r="E10" t="n">
-        <v>868.175060984978</v>
+        <v>846.701689071949</v>
       </c>
       <c r="F10" t="n">
-        <v>1355.57802667731</v>
+        <v>1344.38613336049</v>
       </c>
       <c r="G10" t="n">
         <v>5136.6511162332</v>
       </c>
       <c r="H10" t="n">
-        <v>966.39582458142</v>
+        <v>956.91586016651</v>
       </c>
     </row>
     <row r="11">
@@ -1554,22 +1583,22 @@
         <v>-422718221.670948</v>
       </c>
       <c r="C11" t="n">
-        <v>-249316661.211196</v>
+        <v>-247309496.990056</v>
       </c>
       <c r="D11" t="n">
-        <v>-187279001.693242</v>
+        <v>-183351481.973659</v>
       </c>
       <c r="E11" t="n">
-        <v>-151854309.884923</v>
+        <v>-147370980.053903</v>
       </c>
       <c r="F11" t="n">
-        <v>-112898482.984747</v>
+        <v>-112476763.02446</v>
       </c>
       <c r="G11" t="n">
         <v>2423397568.0545</v>
       </c>
       <c r="H11" t="n">
-        <v>136418178.226449</v>
+        <v>134832733.965596</v>
       </c>
     </row>
     <row r="12">
@@ -1577,25 +1606,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>-131301469.809841</v>
+        <v>-120720367.522153</v>
       </c>
       <c r="C12" t="n">
-        <v>-19773908.5706416</v>
+        <v>-17290728.6469126</v>
       </c>
       <c r="D12" t="n">
-        <v>-9584200.05190419</v>
+        <v>-9199083.43348651</v>
       </c>
       <c r="E12" t="n">
-        <v>-16467349.4991025</v>
+        <v>-13971249.602734</v>
       </c>
       <c r="F12" t="n">
-        <v>-4247814.60424129</v>
+        <v>-4074154.41259218</v>
       </c>
       <c r="G12" t="n">
         <v>2408482.87376139</v>
       </c>
       <c r="H12" t="n">
-        <v>15526093.9664003</v>
+        <v>13216574.2343204</v>
       </c>
     </row>
     <row r="13">
@@ -1606,22 +1635,22 @@
         <v>-0.0000000070924223479098</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.000000000279779978438966</v>
+        <v>-0.000000000262857071767259</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.000000000141658355360436</v>
+        <v>-0.000000000130761341311364</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00000000025880822096539</v>
+        <v>-0.000000000229376184301506</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0000000000570135650840912</v>
+        <v>-0.0000000000552421495224276</v>
       </c>
       <c r="G13" t="n">
         <v>0.000000000115165594031759</v>
       </c>
       <c r="H13" t="n">
-        <v>0.000000000222766413354874</v>
+        <v>0.000000000207614922244831</v>
       </c>
     </row>
     <row r="14">
@@ -1629,25 +1658,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0000000066761954034308</v>
+        <v>-0.00000000517102977273062</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00000000010559887209922</v>
+        <v>-0.000000000087386461837399</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0000000000265132590904378</v>
+        <v>-0.0000000000238892906251516</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.000000000172018490808414</v>
+        <v>-0.000000000118055549151304</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00000000000725538472379065</v>
+        <v>-0.00000000000701875926883767</v>
       </c>
       <c r="G14" t="n">
         <v>0.00000000000611176612752003</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0000000000983434873754293</v>
+        <v>0.0000000000803677025685613</v>
       </c>
     </row>
     <row r="15">
@@ -1658,22 +1687,22 @@
         <v>-2413800.32548477</v>
       </c>
       <c r="C15" t="n">
-        <v>-959914.64377221</v>
+        <v>-946129.996748369</v>
       </c>
       <c r="D15" t="n">
-        <v>-635876.0614944</v>
+        <v>-631581.80410028</v>
       </c>
       <c r="E15" t="n">
-        <v>-617966.49983508</v>
+        <v>-610288.686184024</v>
       </c>
       <c r="F15" t="n">
-        <v>-301512.088185519</v>
+        <v>-300402.87981592</v>
       </c>
       <c r="G15" t="n">
         <v>4208029.07683537</v>
       </c>
       <c r="H15" t="n">
-        <v>658402.555586691</v>
+        <v>645727.116932449</v>
       </c>
     </row>
     <row r="16">
@@ -1684,22 +1713,22 @@
         <v>-328223.450196674</v>
       </c>
       <c r="C16" t="n">
-        <v>-119601.887149657</v>
+        <v>-122959.306736447</v>
       </c>
       <c r="D16" t="n">
-        <v>-64893.1790081519</v>
+        <v>-70596.2598601672</v>
       </c>
       <c r="E16" t="n">
-        <v>115190.337245332</v>
+        <v>126856.071980857</v>
       </c>
       <c r="F16" t="n">
-        <v>-22153.6945455015</v>
+        <v>-26408.77254656</v>
       </c>
       <c r="G16" t="n">
         <v>20992555.0734624</v>
       </c>
       <c r="H16" t="n">
-        <v>97448.1926041555</v>
+        <v>96550.5341898873</v>
       </c>
     </row>
     <row r="17">
@@ -1710,22 +1739,22 @@
         <v>-960822.21716642</v>
       </c>
       <c r="C17" t="n">
-        <v>7496.86535073122</v>
+        <v>7585.39613343624</v>
       </c>
       <c r="D17" t="n">
-        <v>16875.264918781</v>
+        <v>17516.2313098555</v>
       </c>
       <c r="E17" t="n">
-        <v>12650.7173616408</v>
+        <v>12569.766403766</v>
       </c>
       <c r="F17" t="n">
-        <v>29213.7087853915</v>
+        <v>29928.2078231045</v>
       </c>
       <c r="G17" t="n">
         <v>128618.55793744</v>
       </c>
       <c r="H17" t="n">
-        <v>21716.8434346603</v>
+        <v>22342.8116896683</v>
       </c>
     </row>
     <row r="18">
@@ -1733,25 +1762,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>-6114613.07471473</v>
+        <v>-6016891.07497805</v>
       </c>
       <c r="C18" t="n">
-        <v>-2679989.91603235</v>
+        <v>-2619718.36152952</v>
       </c>
       <c r="D18" t="n">
-        <v>-1787304.15427708</v>
+        <v>-1724225.19426618</v>
       </c>
       <c r="E18" t="n">
-        <v>-1706921.07586652</v>
+        <v>-1647401.17036085</v>
       </c>
       <c r="F18" t="n">
-        <v>-720660.960951136</v>
+        <v>-719811.714589014</v>
       </c>
       <c r="G18" t="n">
         <v>8209638.69045956</v>
       </c>
       <c r="H18" t="n">
-        <v>1959328.95508122</v>
+        <v>1899906.64694051</v>
       </c>
     </row>
     <row r="19">
@@ -1762,22 +1791,22 @@
         <v>-1896907.45173721</v>
       </c>
       <c r="C19" t="n">
-        <v>-527854.226817226</v>
+        <v>-555418.162662136</v>
       </c>
       <c r="D19" t="n">
-        <v>-278278.756127293</v>
+        <v>-315429.068109552</v>
       </c>
       <c r="E19" t="n">
-        <v>264114.583495855</v>
+        <v>297543.152812408</v>
       </c>
       <c r="F19" t="n">
-        <v>-108853.318891989</v>
+        <v>-117460.863879871</v>
       </c>
       <c r="G19" t="n">
         <v>60701825.7142045</v>
       </c>
       <c r="H19" t="n">
-        <v>419000.907925238</v>
+        <v>437957.298782266</v>
       </c>
     </row>
     <row r="20">
@@ -1788,22 +1817,22 @@
         <v>-2655196.65845205</v>
       </c>
       <c r="C20" t="n">
-        <v>19726.4398593687</v>
+        <v>19574.2700270798</v>
       </c>
       <c r="D20" t="n">
-        <v>43255.6589657876</v>
+        <v>44610.305849346</v>
       </c>
       <c r="E20" t="n">
-        <v>38551.6662208969</v>
+        <v>37458.1028901261</v>
       </c>
       <c r="F20" t="n">
-        <v>93272.888079805</v>
+        <v>96475.7873589374</v>
       </c>
       <c r="G20" t="n">
         <v>270006.785285659</v>
       </c>
       <c r="H20" t="n">
-        <v>73546.4482204363</v>
+        <v>76901.5173318576</v>
       </c>
     </row>
     <row r="21">
@@ -1814,22 +1843,22 @@
         <v>-377670.229329517</v>
       </c>
       <c r="C21" t="n">
-        <v>-28115.0423538026</v>
+        <v>-23070.4207068028</v>
       </c>
       <c r="D21" t="n">
-        <v>-12317.8033062236</v>
+        <v>-10559.8753436724</v>
       </c>
       <c r="E21" t="n">
-        <v>-25307.8788828087</v>
+        <v>-20837.7938380848</v>
       </c>
       <c r="F21" t="n">
-        <v>-4744.46855460169</v>
+        <v>-4427.65467823153</v>
       </c>
       <c r="G21" t="n">
         <v>120682.438633709</v>
       </c>
       <c r="H21" t="n">
-        <v>23370.5737992009</v>
+        <v>18642.7660285712</v>
       </c>
     </row>
     <row r="22">
@@ -1840,22 +1869,22 @@
         <v>-49494.423254304</v>
       </c>
       <c r="C22" t="n">
-        <v>-4718.13650076538</v>
+        <v>-4489.926513922</v>
       </c>
       <c r="D22" t="n">
-        <v>-2211.2455736255</v>
+        <v>-2061.93138119147</v>
       </c>
       <c r="E22" t="n">
-        <v>-3622.02563760765</v>
+        <v>-3348.10040671611</v>
       </c>
       <c r="F22" t="n">
-        <v>-1001.857289837</v>
+        <v>-961.072461891706</v>
       </c>
       <c r="G22" t="n">
         <v>20322.9325312903</v>
       </c>
       <c r="H22" t="n">
-        <v>3716.27921092838</v>
+        <v>3528.85405203029</v>
       </c>
     </row>
     <row r="23">
@@ -1866,22 +1895,22 @@
         <v>-10226.4804291401</v>
       </c>
       <c r="C23" t="n">
-        <v>-1957.19118759001</v>
+        <v>-1914.87886588901</v>
       </c>
       <c r="D23" t="n">
         <v>-1024.67260188991</v>
       </c>
       <c r="E23" t="n">
-        <v>-969.581371711186</v>
+        <v>-901.334784035381</v>
       </c>
       <c r="F23" t="n">
-        <v>-568.587592291226</v>
+        <v>-552.262515536765</v>
       </c>
       <c r="G23" t="n">
         <v>50090.705827621</v>
       </c>
       <c r="H23" t="n">
-        <v>1388.60359529879</v>
+        <v>1362.61635035225</v>
       </c>
     </row>
     <row r="24">
@@ -1892,22 +1921,22 @@
         <v>-27077.11246331</v>
       </c>
       <c r="C24" t="n">
-        <v>894.395313366653</v>
+        <v>877.56246713866</v>
       </c>
       <c r="D24" t="n">
-        <v>2302.82282132065</v>
+        <v>2146.17728033775</v>
       </c>
       <c r="E24" t="n">
-        <v>4140.08176779739</v>
+        <v>3728.54030995778</v>
       </c>
       <c r="F24" t="n">
-        <v>5537.63186417198</v>
+        <v>4903.62879190793</v>
       </c>
       <c r="G24" t="n">
-        <v>88074.1936271101</v>
+        <v>38856.56951752</v>
       </c>
       <c r="H24" t="n">
-        <v>4643.23655080532</v>
+        <v>4026.06632476927</v>
       </c>
     </row>
     <row r="25">
@@ -1915,25 +1944,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>-24933.6949309505</v>
+        <v>-24388.10042804</v>
       </c>
       <c r="C25" t="n">
-        <v>155.359902720419</v>
+        <v>148.084788875732</v>
       </c>
       <c r="D25" t="n">
-        <v>379.433373609575</v>
+        <v>372.025255046535</v>
       </c>
       <c r="E25" t="n">
-        <v>818.113633257685</v>
+        <v>735.446093787528</v>
       </c>
       <c r="F25" t="n">
-        <v>1085.54871758317</v>
+        <v>1056.66835281681</v>
       </c>
       <c r="G25" t="n">
-        <v>20174.297787889</v>
+        <v>17424.849829695</v>
       </c>
       <c r="H25" t="n">
-        <v>930.188814862755</v>
+        <v>908.583563941075</v>
       </c>
     </row>
     <row r="26">
@@ -1944,22 +1973,22 @@
         <v>-0.0166156316777285</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00148828201106729</v>
+        <v>0.00148130028443935</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0050759174528211</v>
+        <v>0.0049342230092212</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00946307545408682</v>
+        <v>0.00912363122630225</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0121797996049185</v>
+        <v>0.0116417203791951</v>
       </c>
       <c r="G26" t="n">
         <v>0.092757985648147</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0106915175938513</v>
+        <v>0.0101604200947557</v>
       </c>
     </row>
     <row r="27">
@@ -1970,22 +1999,22 @@
         <v>-10.9027728881147</v>
       </c>
       <c r="C27" t="n">
-        <v>0.168027332012449</v>
+        <v>0.1653030498276</v>
       </c>
       <c r="D27" t="n">
-        <v>0.233206263228</v>
+        <v>0.230556175465296</v>
       </c>
       <c r="E27" t="n">
-        <v>0.125253556633626</v>
+        <v>0.117542274184975</v>
       </c>
       <c r="F27" t="n">
-        <v>0.268975384169451</v>
+        <v>0.267316950659274</v>
       </c>
       <c r="G27" t="n">
         <v>0.376100968933102</v>
       </c>
       <c r="H27" t="n">
-        <v>0.100948052157002</v>
+        <v>0.102013900831674</v>
       </c>
     </row>
     <row r="28">
@@ -1996,22 +2025,22 @@
         <v>-0.17941493697866</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0290848715286473</v>
+        <v>-0.026339583930785</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0137405232287995</v>
+        <v>-0.012296699812747</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0209181248637458</v>
+        <v>-0.0187188550392714</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.00693654723593524</v>
+        <v>-0.0064127783426345</v>
       </c>
       <c r="G28" t="n">
         <v>0.0125247228046799</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0221483242927121</v>
+        <v>0.0199268055881505</v>
       </c>
     </row>
     <row r="29">
@@ -2022,22 +2051,22 @@
         <v>-0.5958297114659</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01198522871223</v>
+        <v>0.01191779108973</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01891822154787</v>
+        <v>0.0188965490807203</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0184616772291127</v>
+        <v>0.018274002189702</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0281654918106328</v>
+        <v>0.0277247300267198</v>
       </c>
       <c r="G29" t="n">
         <v>0.0804813653468697</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0161802630984028</v>
+        <v>0.0158069389369898</v>
       </c>
     </row>
     <row r="30">
@@ -2045,25 +2074,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.09669568151996</v>
+        <v>-0.0768383680073901</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0235672267313049</v>
+        <v>-0.0237188667747782</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0140690270800074</v>
+        <v>-0.014240422956379</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00196954377965168</v>
+        <v>0.00379878735025674</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00648008270598475</v>
+        <v>-0.00642475570943851</v>
       </c>
       <c r="G30" t="n">
         <v>2.42187366642834</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0170871440253202</v>
+        <v>0.0172941110653397</v>
       </c>
     </row>
     <row r="31">
@@ -2074,22 +2103,48 @@
         <v>-0.166305449481691</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00125750804166048</v>
+        <v>0.00135182660603646</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00320418833748018</v>
+        <v>0.00343397348691504</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00266182853147252</v>
+        <v>0.0026697958113284</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00631734730672352</v>
+        <v>0.00653921725275695</v>
       </c>
       <c r="G31" t="n">
         <v>0.029198909318277</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00505983926506305</v>
+        <v>0.00518739064672049</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.174568296133969</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.00334219611475955</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.00866868924677502</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0117934270376307</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0177135509937369</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0996568571434058</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0143713548789773</v>
       </c>
     </row>
   </sheetData>
@@ -2137,22 +2192,22 @@
         <v>-0.418584343567514</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0431070377821544</v>
+        <v>0.0423420924388681</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0773478313709621</v>
+        <v>0.0739324493066644</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0916599086890156</v>
+        <v>0.088550504360448</v>
       </c>
       <c r="F2" t="n">
-        <v>0.154797773429134</v>
+        <v>0.1499654212712</v>
       </c>
       <c r="G2" t="n">
         <v>0.291433638360449</v>
       </c>
       <c r="H2" t="n">
-        <v>0.111690735646979</v>
+        <v>0.107623328832331</v>
       </c>
     </row>
     <row r="3">
@@ -2163,22 +2218,22 @@
         <v>-0.467020437615068</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0487339822091732</v>
+        <v>0.0483538851360527</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0846351746787072</v>
+        <v>0.0816707781446481</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0979036661877607</v>
+        <v>0.0946661921417274</v>
       </c>
       <c r="F3" t="n">
-        <v>0.165112810281094</v>
+        <v>0.158722613937278</v>
       </c>
       <c r="G3" t="n">
         <v>0.30361263445977</v>
       </c>
       <c r="H3" t="n">
-        <v>0.116378828071921</v>
+        <v>0.110368728801225</v>
       </c>
     </row>
     <row r="4">
@@ -2189,22 +2244,22 @@
         <v>-0.497548102138032</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0510501896602118</v>
+        <v>0.0506417931418161</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0874972362658138</v>
+        <v>0.084431179062731</v>
       </c>
       <c r="E4" t="n">
-        <v>0.100340565112505</v>
+        <v>0.0970500198654818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.168515205326253</v>
+        <v>0.162258615878883</v>
       </c>
       <c r="G4" t="n">
         <v>0.308433527396614</v>
       </c>
       <c r="H4" t="n">
-        <v>0.117465015666041</v>
+        <v>0.111616822737067</v>
       </c>
     </row>
     <row r="5">
@@ -2215,22 +2270,22 @@
         <v>-1.48906419380108</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.795675299442709</v>
+        <v>-0.758898512699895</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.555272569001944</v>
+        <v>-0.540199751753348</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.557297634597379</v>
+        <v>-0.526581536404385</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.339498985798064</v>
+        <v>-0.314408773381088</v>
       </c>
       <c r="G5" t="n">
         <v>0.5733633183939</v>
       </c>
       <c r="H5" t="n">
-        <v>0.456176313644645</v>
+        <v>0.444489739318807</v>
       </c>
     </row>
     <row r="6">
@@ -2241,22 +2296,22 @@
         <v>-1.49204963144736</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.799390924975621</v>
+        <v>-0.762177357724872</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.55876719386538</v>
+        <v>-0.541915196681379</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.55973456963128</v>
+        <v>-0.528965390768962</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.342102497192896</v>
+        <v>-0.316206133082124</v>
       </c>
       <c r="G6" t="n">
         <v>0.590593965631956</v>
       </c>
       <c r="H6" t="n">
-        <v>0.457288427782725</v>
+        <v>0.445971224642748</v>
       </c>
     </row>
     <row r="7">
@@ -2267,22 +2322,22 @@
         <v>-0.55216979913415</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0558643424769449</v>
+        <v>0.0556995727670021</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0935726166838221</v>
+        <v>0.0902128195837775</v>
       </c>
       <c r="E7" t="n">
-        <v>0.105655516763079</v>
+        <v>0.102272735264575</v>
       </c>
       <c r="F7" t="n">
-        <v>0.176414959475861</v>
+        <v>0.169888245439814</v>
       </c>
       <c r="G7" t="n">
         <v>0.317880629859762</v>
       </c>
       <c r="H7" t="n">
-        <v>0.120550616998916</v>
+        <v>0.114188672672812</v>
       </c>
     </row>
     <row r="8">
@@ -2293,22 +2348,22 @@
         <v>-0.497692477817941</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0511536717818506</v>
+        <v>0.0507452540214246</v>
       </c>
       <c r="D8" t="n">
-        <v>0.087574398517952</v>
+        <v>0.0845013179521226</v>
       </c>
       <c r="E8" t="n">
-        <v>0.100428180750812</v>
+        <v>0.0971291504936042</v>
       </c>
       <c r="F8" t="n">
-        <v>0.168547678238558</v>
+        <v>0.162339382680384</v>
       </c>
       <c r="G8" t="n">
         <v>0.308448676568658</v>
       </c>
       <c r="H8" t="n">
-        <v>0.117394006456707</v>
+        <v>0.111594128658959</v>
       </c>
     </row>
     <row r="9">
@@ -2316,25 +2371,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0000114440295861939</v>
+        <v>-0.0000114411647267332</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00000382335427850933</v>
+        <v>0.00000382320319758378</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000154523642132688</v>
+        <v>0.0000119008036398161</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0000133666473656202</v>
+        <v>0.0000114427229127578</v>
       </c>
       <c r="G9" t="n">
         <v>0.00037957322504667</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0000133666473656202</v>
+        <v>0.0000114427229127578</v>
       </c>
     </row>
     <row r="10">
@@ -2345,22 +2400,22 @@
         <v>-0.303366520792662</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0500711322687935</v>
+        <v>0.0496150128172562</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0852803584535421</v>
+        <v>0.0825285880374843</v>
       </c>
       <c r="E10" t="n">
-        <v>0.100165511918484</v>
+        <v>0.0969342834829605</v>
       </c>
       <c r="F10" t="n">
-        <v>0.16216762286241</v>
+        <v>0.158348166769244</v>
       </c>
       <c r="G10" t="n">
         <v>0.29592108584472</v>
       </c>
       <c r="H10" t="n">
-        <v>0.112096490593617</v>
+        <v>0.108733153951988</v>
       </c>
     </row>
     <row r="11">
@@ -2371,22 +2426,22 @@
         <v>-1.63930897665085</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.9647261796371</v>
+        <v>-0.907547947423111</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.671252275626152</v>
+        <v>-0.650199600399527</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.66007511260385</v>
+        <v>-0.626015383185427</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.411566297152552</v>
+        <v>-0.389731794511802</v>
       </c>
       <c r="G11" t="n">
         <v>1.07667982643614</v>
       </c>
       <c r="H11" t="n">
-        <v>0.553159882484548</v>
+        <v>0.51781615291131</v>
       </c>
     </row>
     <row r="12">
@@ -2397,22 +2452,22 @@
         <v>-1.63659098600167</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.961268199789719</v>
+        <v>-0.903906128234929</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.668110117835357</v>
+        <v>-0.646985050538634</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.657638224113358</v>
+        <v>-0.623631567387381</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.409297578324282</v>
+        <v>-0.387311447878095</v>
       </c>
       <c r="G12" t="n">
         <v>1.04615306991544</v>
       </c>
       <c r="H12" t="n">
-        <v>0.551970621465437</v>
+        <v>0.516594680356834</v>
       </c>
     </row>
     <row r="13">
@@ -2423,22 +2478,22 @@
         <v>-0.313245874128558</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.172267281584474</v>
+        <v>-0.16632298372412</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0904888299980788</v>
+        <v>-0.087188215745126</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.102761968761193</v>
+        <v>-0.0994218910977409</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0531358061209461</v>
+        <v>-0.0529303901770417</v>
       </c>
       <c r="G13" t="n">
         <v>0.528073885013791</v>
       </c>
       <c r="H13" t="n">
-        <v>0.119131475463528</v>
+        <v>0.113392593547079</v>
       </c>
     </row>
     <row r="14">
@@ -2449,22 +2504,22 @@
         <v>-0.308423983957285</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.168499475692581</v>
+        <v>-0.162239077788314</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.087500569340432</v>
+        <v>-0.0844278337742956</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.100325199296195</v>
+        <v>-0.0970381944664678</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0510482736236861</v>
+        <v>-0.0505771644788728</v>
       </c>
       <c r="G14" t="n">
         <v>0.49754713986554</v>
       </c>
       <c r="H14" t="n">
-        <v>0.117451202068894</v>
+        <v>0.111661913309441</v>
       </c>
     </row>
     <row r="15">
@@ -2475,22 +2530,22 @@
         <v>-1.62354948828551</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.945345388545035</v>
+        <v>-0.88055092998654</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.65048229152939</v>
+        <v>-0.631084345207363</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.646869837021385</v>
+        <v>-0.613243607382287</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.398855750772941</v>
+        <v>-0.374254335681657</v>
       </c>
       <c r="G15" t="n">
         <v>0.787661248923636</v>
       </c>
       <c r="H15" t="n">
-        <v>0.546489637772094</v>
+        <v>0.506296594304883</v>
       </c>
     </row>
     <row r="16">
@@ -2501,22 +2556,22 @@
         <v>-1.62083053301925</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.942488334791601</v>
+        <v>-0.875922564879585</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.646641256637991</v>
+        <v>-0.628189541583767</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.644432966402932</v>
+        <v>-0.610859816688761</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.396586774583566</v>
+        <v>-0.371833910225646</v>
       </c>
       <c r="G16" t="n">
         <v>0.770429355901872</v>
       </c>
       <c r="H16" t="n">
-        <v>0.545901560208034</v>
+        <v>0.504088654653938</v>
       </c>
     </row>
     <row r="17">
@@ -2527,22 +2582,22 @@
         <v>-0.448672280093454</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0175713223465127</v>
+        <v>0.0171892513841679</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0243001019897569</v>
+        <v>0.0238718931524564</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0185202074923667</v>
+        <v>0.0179944701130822</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0300452695336244</v>
+        <v>0.0298250860869261</v>
       </c>
       <c r="G17" t="n">
         <v>0.0431862082295393</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0124739471871117</v>
+        <v>0.0126358347027582</v>
       </c>
     </row>
     <row r="18">
@@ -2553,22 +2608,22 @@
         <v>-1.62367540179461</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.945517399476403</v>
+        <v>-0.879236522147103</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.650231472555808</v>
+        <v>-0.630016257146759</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.647256821039657</v>
+        <v>-0.613655946711801</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.399067559731216</v>
+        <v>-0.373462802108304</v>
       </c>
       <c r="G18" t="n">
         <v>0.727782862669855</v>
       </c>
       <c r="H18" t="n">
-        <v>0.546449839745187</v>
+        <v>0.505773720038799</v>
       </c>
     </row>
     <row r="19">
@@ -2579,22 +2634,22 @@
         <v>-1.62095784804419</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.942090276399008</v>
+        <v>-0.874904643780587</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.646389951138032</v>
+        <v>-0.627121670973624</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.64481997298873</v>
+        <v>-0.611272173531814</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.396799197233795</v>
+        <v>-0.371042491477018</v>
       </c>
       <c r="G19" t="n">
         <v>0.710551980852134</v>
       </c>
       <c r="H19" t="n">
-        <v>0.545291079165213</v>
+        <v>0.503862152303569</v>
       </c>
     </row>
     <row r="20">
@@ -2605,22 +2660,22 @@
         <v>-0.543274389526718</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0177104451815945</v>
+        <v>0.0173750001895514</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0250773538310227</v>
+        <v>0.0246541617753513</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0181332028342814</v>
+        <v>0.0175821132946183</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0304473762691037</v>
+        <v>0.0302381540629347</v>
       </c>
       <c r="G20" t="n">
         <v>0.0430135494994888</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0127369310875092</v>
+        <v>0.0128631538733833</v>
       </c>
     </row>
     <row r="21">
@@ -2631,22 +2686,22 @@
         <v>-1.53045551907425</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.829808784579829</v>
+        <v>-0.767931453864895</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.570052604989469</v>
+        <v>-0.550645790533539</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.570456644651465</v>
+        <v>-0.538277795920606</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.33192011184883</v>
+        <v>-0.311633104015306</v>
       </c>
       <c r="G21" t="n">
         <v>0.672261568071165</v>
       </c>
       <c r="H21" t="n">
-        <v>0.497888672731</v>
+        <v>0.456298349849589</v>
       </c>
     </row>
     <row r="22">
@@ -2657,22 +2712,22 @@
         <v>-0.0310816058236019</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.00244752010145133</v>
+        <v>-0.00241856439171628</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.00199713879558816</v>
+        <v>-0.00196708043910521</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.00198170851526449</v>
+        <v>-0.00195078056059321</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.00141896099906369</v>
+        <v>-0.00130350635015108</v>
       </c>
       <c r="G22" t="n">
         <v>0.00471434941635485</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00102855910238764</v>
+        <v>0.0011150580415652</v>
       </c>
     </row>
     <row r="23">
@@ -2680,25 +2735,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.005083937013036</v>
+        <v>-0.00484782137543904</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.00319314290155093</v>
+        <v>-0.00317263017019276</v>
       </c>
       <c r="D23" t="n">
         <v>-0.00261318999902027</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.00170717968834659</v>
+        <v>-0.00164409722256343</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0017636616333806</v>
+        <v>-0.00175458795270711</v>
       </c>
       <c r="G23" t="n">
         <v>0.0660146748541273</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00142948126817033</v>
+        <v>0.00141804221748565</v>
       </c>
     </row>
     <row r="24">
@@ -2706,25 +2761,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.110023355407744</v>
+        <v>-0.0827984941025606</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0315105506029381</v>
+        <v>0.031016895169628</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0451241395582189</v>
+        <v>0.0439936208882554</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0399745039505685</v>
+        <v>0.039483041793669</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0565957428878231</v>
+        <v>0.0551981277578868</v>
       </c>
       <c r="G24" t="n">
         <v>0.08881098962553</v>
       </c>
       <c r="H24" t="n">
-        <v>0.025085192284885</v>
+        <v>0.0241812325882588</v>
       </c>
     </row>
     <row r="25">
@@ -2732,25 +2787,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.110023321272551</v>
+        <v>-0.0827984879387138</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0315105665984842</v>
+        <v>0.0310168767341974</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0451241180938924</v>
+        <v>0.043993678526404</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0399745028324959</v>
+        <v>0.0394830401795905</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0565957377334222</v>
+        <v>0.0551981862027333</v>
       </c>
       <c r="G25" t="n">
         <v>0.0888109471590321</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0250851711349379</v>
+        <v>0.0241813094685359</v>
       </c>
     </row>
     <row r="26">
@@ -2761,22 +2816,22 @@
         <v>-0.247932969276647</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0394452832651204</v>
+        <v>0.039295348884279</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0715988524121971</v>
+        <v>0.069146526326356</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0888072962860722</v>
+        <v>0.0858853687514652</v>
       </c>
       <c r="F26" t="n">
-        <v>0.14711048709018</v>
+        <v>0.143238238470253</v>
       </c>
       <c r="G26" t="n">
         <v>0.282331656229276</v>
       </c>
       <c r="H26" t="n">
-        <v>0.10766520382506</v>
+        <v>0.103942889585974</v>
       </c>
     </row>
     <row r="27">
@@ -2787,22 +2842,22 @@
         <v>-0.148604849856712</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00198704227385191</v>
+        <v>0.00194900193931187</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00262920360755728</v>
+        <v>0.00262042236496371</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00128502515607631</v>
+        <v>0.00119479381540083</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00295460051869585</v>
+        <v>0.0029467728121879</v>
       </c>
       <c r="G27" t="n">
         <v>0.00510154625508608</v>
       </c>
       <c r="H27" t="n">
-        <v>0.000967558244843944</v>
+        <v>0.00099777087287603</v>
       </c>
     </row>
     <row r="28">
@@ -2813,22 +2868,22 @@
         <v>-0.0281704952718385</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0180624658509159</v>
+        <v>-0.0180087849567859</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0134413911262681</v>
+        <v>-0.0132776914511595</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.00967878922484143</v>
+        <v>-0.0093404081671333</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0082658946719153</v>
+        <v>-0.00820834577143237</v>
       </c>
       <c r="G28" t="n">
         <v>0.33835024044667</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00979657117900062</v>
+        <v>0.00980043918535356</v>
       </c>
     </row>
     <row r="29">
@@ -2839,22 +2894,22 @@
         <v>-0.0540023723500036</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00132798995972244</v>
+        <v>0.00128410339991186</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00202315030218791</v>
+        <v>0.00194811148812557</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00167199776228984</v>
+        <v>0.00160712138981323</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00258283333814585</v>
+        <v>0.00251418955921795</v>
       </c>
       <c r="G29" t="n">
         <v>0.00427661527833156</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00125484337842341</v>
+        <v>0.00123008615930609</v>
       </c>
     </row>
     <row r="30">
@@ -2865,22 +2920,22 @@
         <v>-0.0227422594542248</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0142074756169336</v>
+        <v>-0.0141813271871735</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0104625163583172</v>
+        <v>-0.0103609506603273</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00722638415887815</v>
+        <v>-0.00694455685481847</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00625033768816291</v>
+        <v>-0.00621143444697847</v>
       </c>
       <c r="G30" t="n">
         <v>0.30776312874047</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00795713792877067</v>
+        <v>0.00796989274019499</v>
       </c>
     </row>
     <row r="31">
@@ -2891,22 +2946,48 @@
         <v>-0.252936387424177</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0404543036925515</v>
+        <v>0.0400016714773175</v>
       </c>
       <c r="D31" t="n">
-        <v>0.072726369786817</v>
+        <v>0.0705225380332364</v>
       </c>
       <c r="E31" t="n">
-        <v>0.089781080028362</v>
+        <v>0.0868386895605434</v>
       </c>
       <c r="F31" t="n">
-        <v>0.148332250124445</v>
+        <v>0.144177914949657</v>
       </c>
       <c r="G31" t="n">
         <v>0.283769259002909</v>
       </c>
       <c r="H31" t="n">
-        <v>0.107877946431893</v>
+        <v>0.10417624347234</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.252747676129227</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0397421893687082</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0697302472267962</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0861925530926607</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.143627991039134</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.282781340280271</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.103885801670425</v>
       </c>
     </row>
   </sheetData>
@@ -2925,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -2942,16 +3023,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0833333333333</v>
+        <v>15.952380952381</v>
       </c>
     </row>
     <row r="3">
@@ -2959,16 +3040,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5454545454545</v>
+        <v>15.952380952381</v>
       </c>
     </row>
     <row r="4">
@@ -2976,7 +3057,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="C4" t="n">
         <v>21</v>
@@ -2985,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>17.3809523809524</v>
+        <v>15.952380952381</v>
       </c>
     </row>
     <row r="5">
@@ -2993,16 +3074,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="6">
@@ -3010,16 +3091,16 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="7">
@@ -3027,16 +3108,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="8">
@@ -3044,16 +3125,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="9">
@@ -3061,16 +3142,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>4.75862068965517</v>
+        <v>4.64814814814815</v>
       </c>
     </row>
     <row r="10">
@@ -3078,16 +3159,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="11">
@@ -3095,16 +3176,16 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="12">
@@ -3112,16 +3193,16 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="13">
@@ -3129,16 +3210,16 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0604395604395604</v>
+        <v>0.0626865671641791</v>
       </c>
     </row>
     <row r="14">
@@ -3149,13 +3230,13 @@
         <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0575342465753425</v>
+        <v>0.0626865671641791</v>
       </c>
     </row>
     <row r="15">
@@ -3163,16 +3244,16 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="16">
@@ -3180,16 +3261,16 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="17">
@@ -3197,16 +3278,16 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="18">
@@ -3214,16 +3295,16 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="19">
@@ -3231,16 +3312,16 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="20">
@@ -3248,16 +3329,16 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="21">
@@ -3265,16 +3346,16 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="22">
@@ -3282,16 +3363,16 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.046070460704607</v>
+        <v>0.0470588235294118</v>
       </c>
     </row>
     <row r="23">
@@ -3299,16 +3380,16 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="24">
@@ -3316,16 +3397,16 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="25">
@@ -3333,16 +3414,16 @@
         <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="26">
@@ -3350,16 +3431,16 @@
         <v>32</v>
       </c>
       <c r="B26" t="n">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>15.0833333333333</v>
+        <v>15.952380952381</v>
       </c>
     </row>
     <row r="27">
@@ -3367,16 +3448,16 @@
         <v>33</v>
       </c>
       <c r="B27" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>15.7826086956522</v>
+        <v>15.1818181818182</v>
       </c>
     </row>
     <row r="28">
@@ -3384,16 +3465,16 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="29">
@@ -3401,16 +3482,16 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>16.5454545454545</v>
+        <v>15.952380952381</v>
       </c>
     </row>
     <row r="30">
@@ -3418,16 +3499,16 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="n">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0633608815426997</v>
+        <v>0.0658682634730539</v>
       </c>
     </row>
     <row r="31">
@@ -3435,16 +3516,33 @@
         <v>37</v>
       </c>
       <c r="B31" t="n">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>15.0833333333333</v>
+        <v>15.952380952381</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="n">
+        <v>335</v>
+      </c>
+      <c r="C32" t="n">
+        <v>21</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15.952380952381</v>
       </c>
     </row>
   </sheetData>
